--- a/03_Outputs/Cartama/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Cartama/03_Ordenamiento/ordenamiento.xlsx
@@ -30,6 +30,7 @@
     <sheet name="_fig_12" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="_fig_13" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="_fig_14" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="_mapa03_deficit_vivienda" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
 </workbook>
 </file>
@@ -147,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -193,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -202,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,12 +1004,12 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="72.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1057,35 +1426,35 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -1110,7 +1479,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="112">
+      <c r="E2" s="138">
         <v>0.244002550111255</v>
       </c>
     </row>
@@ -1133,7 +1502,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="112" t="inlineStr">
+      <c r="E3" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1158,7 +1527,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="138">
         <v>0.201125740628123</v>
       </c>
     </row>
@@ -1181,7 +1550,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="138">
         <v>0.305831475741573</v>
       </c>
     </row>
@@ -1204,7 +1573,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="112" t="inlineStr">
+      <c r="E6" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1229,7 +1598,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="138">
         <v>0.249408944781577</v>
       </c>
     </row>
@@ -1252,7 +1621,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="112" t="inlineStr">
+      <c r="E8" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1277,7 +1646,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="112" t="inlineStr">
+      <c r="E9" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1302,7 +1671,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="112" t="inlineStr">
+      <c r="E10" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1327,7 +1696,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="112" t="inlineStr">
+      <c r="E11" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1352,7 +1721,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="138">
         <v>0.382793184431894</v>
       </c>
     </row>
@@ -1368,17 +1737,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1446,17 +1815,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1584,23 +1953,22 @@
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2113,23 +2481,23 @@
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2642,17 +3010,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2780,17 +3148,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2918,23 +3286,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3132,23 +3500,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3496,17 +3864,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3634,101 +4002,101 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -3753,50 +4121,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.993980190542582</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.942488171215891</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.70975459028938</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.581299603770788</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.252589111509076</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0.398860640697428</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3821,50 +4189,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.987077258108712</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.967427782344712</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.776558646649072</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.929123941793219</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.356370512986919</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.488901628232308</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3889,50 +4257,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.929718471114551</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.763806088082304</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.884399277575824</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.454855100508185</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0.680792293834976</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3957,50 +4325,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>0.979967570049649</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.977931131795701</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.892370909983769</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.975977681689036</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.346494647623239</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4025,50 +4393,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>0.977032816551021</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.925338350043211</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.558491908572742</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.744407717265875</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.262536154779924</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0.354185243604538</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4093,50 +4461,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="15">
         <v>0.701679995451789</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="19">
         <v>0.565380533656762</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="20">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>0.755699476955731</v>
       </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="24">
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="27">
         <v>0.392591153729533</v>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="28">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="31">
         <v>0.505708952395391</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4161,50 +4529,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>0.995301989472745</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" s="12">
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" s="15">
         <v>0.981207957890981</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" s="19">
         <v>0.905084866730881</v>
       </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" s="20">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="23">
         <v>0.9238769088399</v>
       </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M8" s="24">
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="27">
         <v>0.316802025007145</v>
       </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O8" s="28">
+      <c r="N8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="31">
         <v>0.625037477450777</v>
       </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4229,50 +4597,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" s="15">
         <v>0.946956418864412</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I9" s="16">
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" s="19">
         <v>0.59017197247855</v>
       </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K9" s="20">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" s="23">
         <v>0.906183690633409</v>
       </c>
-      <c r="L9" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M9" s="24">
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="27">
         <v>0.426644566472535</v>
       </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O9" s="28">
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="31">
         <v>0.5975067949838</v>
       </c>
-      <c r="P9" s="30" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4297,50 +4665,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>0.991277769494558</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" s="12">
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" s="15">
         <v>0.83137021022812</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" s="19">
         <v>0.659967490798318</v>
       </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K10" s="20">
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="23">
         <v>0.77883876079133</v>
       </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M10" s="24">
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="27">
         <v>0.407030114863897</v>
       </c>
-      <c r="N10" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O10" s="28">
+      <c r="N10" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" s="31">
         <v>0.647545584507845</v>
       </c>
-      <c r="P10" s="30" t="inlineStr">
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4365,50 +4733,50 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>0.995490500480521</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" s="12">
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" s="15">
         <v>0.972943002883123</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" s="16">
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" s="19">
         <v>0.761564875685259</v>
       </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K11" s="20">
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" s="23">
         <v>0.777720807111567</v>
       </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M11" s="24">
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="27">
         <v>0.290238415455871</v>
       </c>
-      <c r="N11" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O11" s="28">
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" s="31">
         <v>0.593613995251088</v>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4433,262 +4801,262 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>0.995307283504804</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" s="12">
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" s="15">
         <v>0.984177772972204</v>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I12" s="16">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" s="19">
         <v>0.861627627965673</v>
       </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" s="20">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" s="23">
         <v>0.974792339981811</v>
       </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M12" s="24">
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="27">
         <v>0.368396944642757</v>
       </c>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O12" s="28">
+      <c r="N12" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" s="31">
         <v>0.421302851844501</v>
       </c>
-      <c r="P12" s="30" t="inlineStr">
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA CARTAMA (ECV oficial)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F13" s="11">
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="14">
         <v>0.993078934423914</v>
       </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H13" s="15">
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H13" s="18">
         <v>0.941258393371253</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J13" s="19">
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" s="22">
         <v>0.760810577022788</v>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L13" s="23">
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" s="26">
         <v>0.881406935071191</v>
       </c>
-      <c r="M13" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N13" s="27">
+      <c r="M13" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" s="30">
         <v>0.360101424920487</v>
       </c>
-      <c r="O13" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" s="31">
+      <c r="O13" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" s="34">
         <v>0.517598423661524</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN SUROESTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F14" s="11">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" s="14">
         <v>0.994561336576182</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H14" s="15">
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H14" s="18">
         <v>0.926735678284499</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" s="19">
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" s="22">
         <v>0.771139137032332</v>
       </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L14" s="23">
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" s="26">
         <v>0.864272857079277</v>
       </c>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N14" s="27">
+      <c r="M14" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" s="30">
         <v>0.387591557264862</v>
       </c>
-      <c r="O14" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P14" s="31">
+      <c r="O14" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" s="34">
         <v>0.486570180771037</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F15" s="11">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H15" s="15">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H15" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" s="19">
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L15" s="23">
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N15" s="27">
+      <c r="M15" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O15" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P15" s="31">
+      <c r="O15" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -4704,17 +5072,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4842,17 +5210,17 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4970,17 +5338,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5108,17 +5476,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5131,7 +5499,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>403.422982885086</v>
+        <v>122.693931984886</v>
       </c>
     </row>
     <row r="3">
@@ -5141,7 +5509,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>535.434263853642</v>
+        <v>173.970682928677</v>
       </c>
     </row>
     <row r="4">
@@ -5151,7 +5519,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>406.997774067891</v>
+        <v>148.094045631608</v>
       </c>
     </row>
     <row r="5">
@@ -5161,7 +5529,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>323.318696556506</v>
+        <v>140.16639704183</v>
       </c>
     </row>
     <row r="6">
@@ -5171,7 +5539,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>202.508412358519</v>
+        <v>54.1449984704803</v>
       </c>
     </row>
     <row r="7">
@@ -5181,7 +5549,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>175.521926433227</v>
+        <v>52.0269523914724</v>
       </c>
     </row>
     <row r="8">
@@ -5191,7 +5559,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>438.887003732609</v>
+        <v>120.25788937903</v>
       </c>
     </row>
     <row r="9">
@@ -5201,7 +5569,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>319.359481827996</v>
+        <v>75.6866978529447</v>
       </c>
     </row>
     <row r="10">
@@ -5211,7 +5579,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>447.834045149481</v>
+        <v>121.873093349603</v>
       </c>
     </row>
     <row r="11">
@@ -5221,7 +5589,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>263.33035448317</v>
+        <v>86.9824247840334</v>
       </c>
     </row>
     <row r="12">
@@ -5231,7 +5599,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>721.720915243313</v>
+        <v>143.973573960683</v>
       </c>
     </row>
   </sheetData>
@@ -5246,17 +5614,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5269,7 +5637,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.865013774104683</v>
+        <v>0.864130434782609</v>
       </c>
     </row>
     <row r="3">
@@ -5279,7 +5647,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.686757215619694</v>
+        <v>0.721750489875898</v>
       </c>
     </row>
     <row r="4">
@@ -5289,7 +5657,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.57819176209195</v>
+        <v>0.635039924847346</v>
       </c>
     </row>
     <row r="5">
@@ -5299,7 +5667,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.763045032165833</v>
+        <v>0.831821929101402</v>
       </c>
     </row>
     <row r="6">
@@ -5309,7 +5677,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.314954682779456</v>
+        <v>0.338983050847458</v>
       </c>
     </row>
     <row r="7">
@@ -5319,7 +5687,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.697293895531781</v>
+        <v>0.607218683651805</v>
       </c>
     </row>
     <row r="8">
@@ -5329,7 +5697,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.749497448585124</v>
+        <v>0.723476297968397</v>
       </c>
     </row>
     <row r="9">
@@ -5339,7 +5707,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.578779342723005</v>
+        <v>0.496830427892235</v>
       </c>
     </row>
     <row r="10">
@@ -5349,7 +5717,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.49625340599455</v>
+        <v>0.48936170212766</v>
       </c>
     </row>
     <row r="11">
@@ -5359,7 +5727,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.750565610859729</v>
+        <v>0.724315068493151</v>
       </c>
     </row>
     <row r="12">
@@ -5369,7 +5737,223 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.799620450993525</v>
+        <v>0.706211527700056</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="168" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="168" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="168" t="inlineStr">
+        <is>
+          <t>Déficit cuantitativo de vivienda</t>
+        </is>
+      </c>
+      <c r="D1" s="168" t="inlineStr">
+        <is>
+          <t>Déficit cualitativo de vivienda</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5145</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.0755226800158652</v>
+      </c>
+      <c r="D2">
+        <v>0.211171231490909</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5282</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.0902601710437128</v>
+      </c>
+      <c r="D3">
+        <v>0.203870612844391</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5368</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.0157513810372868</v>
+      </c>
+      <c r="D4">
+        <v>0.163141024305732</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5390</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.0696006683694781</v>
+      </c>
+      <c r="D5">
+        <v>0.308551565724369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5467</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.0358908000759312</v>
+      </c>
+      <c r="D6">
+        <v>0.200918961709605</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5576</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.0169562992722862</v>
+      </c>
+      <c r="D7">
+        <v>0.452352609485622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5679</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.0187920421090195</v>
+      </c>
+      <c r="D8">
+        <v>0.170882796023641</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5789</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.036812558713753</v>
+      </c>
+      <c r="D9">
+        <v>0.219723542553305</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5792</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.0147351172465408</v>
+      </c>
+      <c r="D10">
+        <v>0.380593101084738</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5856</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.081348007349216</v>
+      </c>
+      <c r="D11">
+        <v>0.148268733850129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5861</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.0102574717614961</v>
+      </c>
+      <c r="D12">
+        <v>0.17618422465465</v>
       </c>
     </row>
   </sheetData>
@@ -5384,47 +5968,47 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="61.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -5449,13 +6033,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0.244138614833814</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.133322034968044</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.432221132216294</v>
       </c>
     </row>
@@ -5478,13 +6062,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.276347020345717</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.567509284355768</v>
       </c>
     </row>
@@ -5507,13 +6091,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0.143697606183459</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.316236578206068</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.646129099202138</v>
       </c>
     </row>
@@ -5536,13 +6120,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0.762896966463668</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.0717247564355766</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.055760747917827</v>
       </c>
     </row>
@@ -5565,13 +6149,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.495503088796899</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.794664607550323</v>
       </c>
     </row>
@@ -5594,13 +6178,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="38">
         <v>0</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="40">
         <v>0.426997659319249</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="42">
         <v>0.538748426302271</v>
       </c>
     </row>
@@ -5623,13 +6207,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="38">
         <v>0.331243987264544</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="40">
         <v>0.146335498304644</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="42">
         <v>0.49577439183002</v>
       </c>
     </row>
@@ -5652,13 +6236,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="38">
         <v>0.0495477012594288</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="40">
         <v>0.187057685407582</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="42">
         <v>0.373587663452934</v>
       </c>
     </row>
@@ -5681,13 +6265,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="38">
         <v>0.237741974659209</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="40">
         <v>0.429235352709069</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="42">
         <v>0.377088329347278</v>
       </c>
     </row>
@@ -5710,13 +6294,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="38">
         <v>0.209318096145112</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="40">
         <v>0.30348567951477</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="42">
         <v>0.277510060111701</v>
       </c>
     </row>
@@ -5739,44 +6323,44 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="38">
         <v>0.116998193011675</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="40">
         <v>0.218676157590937</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="42">
         <v>0.426392797110417</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por área del municipio)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="33">
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="39">
         <v>0.151805971774474</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="41">
         <v>0.262364577579315</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="43">
         <v>0.472718766221748</v>
       </c>
     </row>
@@ -5792,47 +6376,47 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -5857,13 +6441,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>4.58145156635787</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>2.5018919942269</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>8.11096673319473</v>
       </c>
     </row>
@@ -5886,13 +6470,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>0</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>2.72185874437185</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>5.58963909291847</v>
       </c>
     </row>
@@ -5915,13 +6499,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>2.05368839741771</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>4.51957001059383</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>9.23430716424932</v>
       </c>
     </row>
@@ -5944,13 +6528,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>4.86310808331718</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>0.457211469082988</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>0.355448449595992</v>
       </c>
     </row>
@@ -5973,13 +6557,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>5.40210443226703</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>8.66364165163244</v>
       </c>
     </row>
@@ -6002,13 +6586,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <v>0</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="49">
         <v>3.53021202749752</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="51">
         <v>4.45411381729768</v>
       </c>
     </row>
@@ -6031,13 +6615,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="47">
         <v>2.35034719491149</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="49">
         <v>1.0383259505979</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="51">
         <v>3.51777540407408</v>
       </c>
     </row>
@@ -6060,13 +6644,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="47">
         <v>0.733918579522148</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="49">
         <v>2.77076649922096</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="51">
         <v>5.53371640498054</v>
       </c>
     </row>
@@ -6089,13 +6673,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="47">
         <v>4.39983565966736</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="49">
         <v>7.94375925389875</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="51">
         <v>6.97868637073791</v>
       </c>
     </row>
@@ -6118,13 +6702,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="47">
         <v>3.84161838873697</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="49">
         <v>5.56987756249235</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="51">
         <v>5.09314660135996</v>
       </c>
     </row>
@@ -6147,44 +6731,44 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="47">
         <v>1.37666489008705</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="49">
         <v>2.57306357222583</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="51">
         <v>5.01717144562522</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por población)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="39">
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="48">
         <v>1.73503584721854</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="50">
         <v>2.9887212669511</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="52">
         <v>5.38452380688663</v>
       </c>
     </row>
@@ -6200,71 +6784,71 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -6289,19 +6873,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>180952376000</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>60446781000</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>120505595000</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.334048009405524</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.665951990594476</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -6334,19 +6918,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>676138456000</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>328995724000</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>347142732000</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.486580405360052</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.513419594639948</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -6379,19 +6963,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>1857635659002</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>559214794002</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>1298420865000</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.301035777006151</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.698964222993849</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -6424,19 +7008,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>632418190000</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>323247541000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>309170649000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.511129417387568</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.488870582612432</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -6469,19 +7053,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>234479508000</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>40928771000</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>193550737000</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.174551590239604</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.825448409760396</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -6514,19 +7098,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="56">
         <v>303724525000</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="58">
         <v>174941851000</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="60">
         <v>128782674000</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="62">
         <v>0.575988557394237</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <v>0.424011442605763</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -6559,19 +7143,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <v>1097406282000</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="58">
         <v>404699201000</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="60">
         <v>692707081000</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="62">
         <v>0.368777915379201</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="64">
         <v>0.631222084620799</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -6604,19 +7188,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="56">
         <v>1055339168000</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="58">
         <v>407164238000</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="60">
         <v>648174930000</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="62">
         <v>0.385813632570491</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="64">
         <v>0.614186367429509</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -6649,19 +7233,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="56">
         <v>608241222000</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="58">
         <v>86298367000</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="60">
         <v>521942855000</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="62">
         <v>0.141881812476038</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="64">
         <v>0.858118187523962</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -6694,19 +7278,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="56">
         <v>571264272000</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="58">
         <v>120249886000</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="60">
         <v>451014386000</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="62">
         <v>0.210497823676255</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="64">
         <v>0.789502176323745</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -6739,19 +7323,19 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="56">
         <v>1111841673101</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="58">
         <v>362913121004</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="60">
         <v>748928552097</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="62">
         <v>0.326407194283167</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="64">
         <v>0.673592805716833</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -6766,47 +7350,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="45">
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="57">
         <v>8329441331103</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="59">
         <v>2869100275006</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="61">
         <v>5460341056097</v>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="63">
         <v>0.344452906378304</v>
       </c>
-      <c r="I13" s="53">
+      <c r="I13" s="65">
         <v>0.655547093621696</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6824,100 +7408,100 @@
   <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="57.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -6942,40 +7526,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>31.0489561955095</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>6.61130195664301</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>50.5516944215977</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>58.0035826303653</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>42.3516692636171</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>43.9841927965066</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>8.40836459699571</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>43.9447317177064</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>52.3931843463464</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>20.8960529620214</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>14.3937434588044</v>
       </c>
     </row>
@@ -6998,40 +7582,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>31.4435255098661</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>12.2095987968943</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>31.9719499737064</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>66.5145268273953</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>53.2176440181042</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>43.3077858721766</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>17.4632865723491</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>40.997397294198</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>45.1620501690815</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>16.6465348901536</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>18.3880061944678</v>
       </c>
     </row>
@@ -7054,40 +7638,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>33.7272491764876</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>12.6150924218961</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>46.6216673664512</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>64.6166557299676</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>51.0231117023124</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>52.1392248876516</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>14.3471138350548</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>43.3541149598071</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>39.9792042556701</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>23.9930627191368</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>22.3104930634161</v>
       </c>
     </row>
@@ -7110,40 +7694,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>32.8379839074844</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>10.1509234331262</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>42.1976305639712</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>61.0904949224259</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>55.808654370219</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>50.1719799011839</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>15.6579008671197</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>42.808130814513</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>53.256748623508</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>16.3120455241306</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>13.7633139621308</v>
       </c>
     </row>
@@ -7166,40 +7750,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>30.8153650257629</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>2.44798331169519</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>44.0630284784718</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>65.7186794372332</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>48.9075922035979</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>52.8352486507012</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>6.0532891355873</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>29.5675751312616</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>51.3840645416186</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>21.3757675339518</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>16.6157868592727</v>
       </c>
     </row>
@@ -7222,40 +7806,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="69">
         <v>30.4121440829347</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="71">
         <v>2.17962982077034</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="73">
         <v>41.5474003854816</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="75">
         <v>57.4249419314044</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="77">
         <v>50.1394463868895</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="79">
         <v>0</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="81">
         <v>45.3986420217875</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="83">
         <v>3.52305290299596</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="85">
         <v>45.911147573265</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="87">
         <v>50.1041254215598</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="89">
         <v>22.013962622208</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="91">
         <v>16.2912358459192</v>
       </c>
     </row>
@@ -7278,40 +7862,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="69">
         <v>33.3898603838625</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="71">
         <v>16.1083951332261</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="73">
         <v>39.3627784317682</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="75">
         <v>64.8624071815098</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="77">
         <v>56.5530845005472</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="79">
         <v>0</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="81">
         <v>48.5344843198161</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="83">
         <v>15.4563583409533</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="85">
         <v>42.8532278145658</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="87">
         <v>46.457054434737</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="89">
         <v>17.1410059678325</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="91">
         <v>19.9596680975312</v>
       </c>
     </row>
@@ -7334,40 +7918,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="69">
         <v>32.3798368929074</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="71">
         <v>9.10285352658306</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="73">
         <v>47.4244881170707</v>
       </c>
-      <c r="H9" s="60">
+      <c r="H9" s="75">
         <v>61.0652721268169</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="77">
         <v>48.6831982728991</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="79">
         <v>0</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="81">
         <v>51.8067342015557</v>
       </c>
-      <c r="L9" s="68">
+      <c r="L9" s="83">
         <v>7.82742232516734</v>
       </c>
-      <c r="M9" s="70">
+      <c r="M9" s="85">
         <v>37.7491921452893</v>
       </c>
-      <c r="N9" s="72">
+      <c r="N9" s="87">
         <v>46.9674287727742</v>
       </c>
-      <c r="O9" s="74">
+      <c r="O9" s="89">
         <v>23.9301000916166</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="91">
         <v>21.6215162422087</v>
       </c>
     </row>
@@ -7390,40 +7974,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="69">
         <v>31.8314480145107</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="71">
         <v>5.53027028442098</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="73">
         <v>41.3979317791899</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="75">
         <v>55.0936854573693</v>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="77">
         <v>50.7401999281876</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="79">
         <v>0</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="81">
         <v>46.0153795298561</v>
       </c>
-      <c r="L10" s="68">
+      <c r="L10" s="83">
         <v>12.2871671317161</v>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="85">
         <v>37.3702746032302</v>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="87">
         <v>50.2141081320076</v>
       </c>
-      <c r="O10" s="74">
+      <c r="O10" s="89">
         <v>33.4408118130307</v>
       </c>
-      <c r="P10" s="76">
+      <c r="P10" s="91">
         <v>18.0560995006092</v>
       </c>
     </row>
@@ -7446,40 +8030,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="69">
         <v>30.4776336976088</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="71">
         <v>5.93160500974253</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="73">
         <v>37.4530054399471</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="75">
         <v>58.679784952892</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="77">
         <v>46.1813406231912</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="79">
         <v>0</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="81">
         <v>55.2932976987275</v>
       </c>
-      <c r="L11" s="68">
+      <c r="L11" s="83">
         <v>13.1541392114179</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="85">
         <v>34.3423455980244</v>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="87">
         <v>46.9891004567391</v>
       </c>
-      <c r="O11" s="74">
+      <c r="O11" s="89">
         <v>19.2377908837052</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="91">
         <v>17.9915607993102</v>
       </c>
     </row>
@@ -7502,156 +8086,156 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="69">
         <v>34.3082348555409</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="71">
         <v>20.5292355148143</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="73">
         <v>44.4719918376713</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="75">
         <v>61.148196916241</v>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="77">
         <v>55.7144874921883</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="79">
         <v>0</v>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="81">
         <v>56.5221316793747</v>
       </c>
-      <c r="L12" s="68">
+      <c r="L12" s="83">
         <v>14.3768586988592</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="85">
         <v>47.639455015546</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="87">
         <v>42.4961224764035</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="89">
         <v>16.8767082348682</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="91">
         <v>17.6153955449829</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por población 2022)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="55">
+      <c r="C13" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="70">
         <v>32.3701420057893</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="72">
         <v>11.2924366669912</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="74">
         <v>41.1144865314911</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="76">
         <v>62.686484325158</v>
       </c>
-      <c r="I13" s="63">
+      <c r="I13" s="78">
         <v>52.2209816611453</v>
       </c>
-      <c r="J13" s="65">
+      <c r="J13" s="80">
         <v>0</v>
       </c>
-      <c r="K13" s="67">
+      <c r="K13" s="82">
         <v>49.2021191792492</v>
       </c>
-      <c r="L13" s="69">
+      <c r="L13" s="84">
         <v>12.9493202206851</v>
       </c>
-      <c r="M13" s="71">
+      <c r="M13" s="86">
         <v>41.2609354543226</v>
       </c>
-      <c r="N13" s="73">
+      <c r="N13" s="88">
         <v>46.577505240713</v>
       </c>
-      <c r="O13" s="75">
+      <c r="O13" s="90">
         <v>20.0219372389742</v>
       </c>
-      <c r="P13" s="77">
+      <c r="P13" s="92">
         <v>18.7453555449525</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN SUROESTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>SUROESTE</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="55">
+      <c r="C14" s="68" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D14" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="70">
         <v>32.1550527640492</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="72">
         <v>9.66086315440455</v>
       </c>
-      <c r="G14" s="59">
+      <c r="G14" s="74">
         <v>39.861949543529</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="76">
         <v>61.5176609510362</v>
       </c>
-      <c r="I14" s="63">
+      <c r="I14" s="78">
         <v>50.6392818625235</v>
       </c>
-      <c r="J14" s="65">
+      <c r="J14" s="80">
         <v>0</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="82">
         <v>48.3209708685314</v>
       </c>
-      <c r="L14" s="69">
+      <c r="L14" s="84">
         <v>12.3051327642436</v>
       </c>
-      <c r="M14" s="71">
+      <c r="M14" s="86">
         <v>44.0516237468582</v>
       </c>
-      <c r="N14" s="73">
+      <c r="N14" s="88">
         <v>45.5289271517348</v>
       </c>
-      <c r="O14" s="75">
+      <c r="O14" s="90">
         <v>21.3333390035517</v>
       </c>
-      <c r="P14" s="77">
+      <c r="P14" s="92">
         <v>20.4858313581283</v>
       </c>
     </row>
@@ -7667,101 +8251,101 @@
   <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -7786,42 +8370,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>34.12</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>77.72</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>33.33</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>29.17</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>58.25</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>0</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>0</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>41.67</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>12</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100" t="inlineStr">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7846,42 +8430,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>51.96</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>77.72</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>75</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>22.22</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>75</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>33.33</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>64</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>22.22</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>62.2</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>24</v>
       </c>
-      <c r="O3" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="O3" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7906,42 +8490,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>48.7</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>41.75</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>0</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>25</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>0</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>0</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>0</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>62.67</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>0</v>
       </c>
-      <c r="O4" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7966,42 +8550,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>48.43</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>33.42</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>66.5</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>19.05</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>33.33</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>0</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>0</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>13.89</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>74.67</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>24.14</v>
       </c>
-      <c r="O5" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" s="100" t="inlineStr">
+      <c r="O5" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8026,42 +8610,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>54.19</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>58.42</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>0</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>0</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>25</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>33.33</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>44</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>0</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>74.67</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>36</v>
       </c>
-      <c r="O6" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="O6" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8086,40 +8670,40 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="96">
         <v>74.45</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="98">
         <v>94.5</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="100">
         <v>91.67</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="102">
         <v>51.52</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="104">
         <v>91.67</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="106">
         <v>80</v>
       </c>
-      <c r="K7" s="90">
+      <c r="K7" s="108">
         <v>100</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="110">
         <v>13.89</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="112">
         <v>84.15</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="114">
         <v>58.62</v>
       </c>
-      <c r="O7" s="98">
+      <c r="O7" s="116">
         <v>100</v>
       </c>
-      <c r="P7" s="100" t="inlineStr">
+      <c r="P7" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8144,42 +8728,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="96">
         <v>50.28</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="98">
         <v>63.89</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="100">
         <v>0</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="102">
         <v>16.67</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="104">
         <v>25</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="106">
         <v>75</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="108">
         <v>44</v>
       </c>
-      <c r="L8" s="92">
+      <c r="L8" s="110">
         <v>30.56</v>
       </c>
-      <c r="M8" s="94">
+      <c r="M8" s="112">
         <v>62.16</v>
       </c>
-      <c r="N8" s="96">
+      <c r="N8" s="114">
         <v>48.28</v>
       </c>
-      <c r="O8" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" s="100" t="inlineStr">
+      <c r="O8" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8204,42 +8788,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="96">
         <v>47.09</v>
       </c>
-      <c r="F9" s="80">
+      <c r="F9" s="98">
         <v>33.33</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="100">
         <v>0</v>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="102">
         <v>16.67</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="104">
         <v>25</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="106">
         <v>0</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="108">
         <v>40</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="110">
         <v>0</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="112">
         <v>61.33</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="114">
         <v>0</v>
       </c>
-      <c r="O9" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" s="100" t="inlineStr">
+      <c r="O9" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8264,42 +8848,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="96">
         <v>60.96</v>
       </c>
-      <c r="F10" s="80">
+      <c r="F10" s="98">
         <v>63.89</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="100">
         <v>58.25</v>
       </c>
-      <c r="H10" s="84">
+      <c r="H10" s="102">
         <v>13.33</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="104">
         <v>59.09</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="106">
         <v>0</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="108">
         <v>72</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="110">
         <v>0</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="112">
         <v>97.33</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="114">
         <v>8</v>
       </c>
-      <c r="O10" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" s="100" t="inlineStr">
+      <c r="O10" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8324,42 +8908,42 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="96">
         <v>37.29</v>
       </c>
-      <c r="F11" s="80">
+      <c r="F11" s="98">
         <v>58.42</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="100">
         <v>0</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="102">
         <v>16.67</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="104">
         <v>26.6</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="106">
         <v>25</v>
       </c>
-      <c r="K11" s="90">
+      <c r="K11" s="108">
         <v>0</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="110">
         <v>0</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="112">
         <v>65</v>
       </c>
-      <c r="N11" s="96">
+      <c r="N11" s="114">
         <v>20.69</v>
       </c>
-      <c r="O11" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" s="100" t="inlineStr">
+      <c r="O11" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8384,162 +8968,162 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="96">
         <v>37.87</v>
       </c>
-      <c r="F12" s="80">
+      <c r="F12" s="98">
         <v>50.08</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="100">
         <v>58.17</v>
       </c>
-      <c r="H12" s="84">
+      <c r="H12" s="102">
         <v>0</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="104">
         <v>33.25</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="106">
         <v>16.67</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="108">
         <v>56</v>
       </c>
-      <c r="L12" s="92">
+      <c r="L12" s="110">
         <v>0</v>
       </c>
-      <c r="M12" s="94">
+      <c r="M12" s="112">
         <v>46.67</v>
       </c>
-      <c r="N12" s="96">
+      <c r="N12" s="114">
         <v>20.69</v>
       </c>
-      <c r="O12" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P12" s="100" t="inlineStr">
+      <c r="O12" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por población 2024)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="79">
+      <c r="C13" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="97">
         <v>49.9053495576476</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="99">
         <v>59.3210302415925</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="101">
         <v>31.6394413174162</v>
       </c>
-      <c r="H13" s="85">
+      <c r="H13" s="103">
         <v>16.5438640617025</v>
       </c>
-      <c r="I13" s="87">
+      <c r="I13" s="105">
         <v>41.594333068678</v>
       </c>
-      <c r="J13" s="89">
+      <c r="J13" s="107">
         <v>32.5569725089321</v>
       </c>
-      <c r="K13" s="91">
+      <c r="K13" s="109">
         <v>42.3005444337322</v>
       </c>
-      <c r="L13" s="93">
+      <c r="L13" s="111">
         <v>11.8823315658141</v>
       </c>
-      <c r="M13" s="95">
+      <c r="M13" s="113">
         <v>64.6415312907616</v>
       </c>
-      <c r="N13" s="97">
+      <c r="N13" s="115">
         <v>24.6625382804968</v>
       </c>
-      <c r="O13" s="99">
+      <c r="O13" s="117">
         <v>100</v>
       </c>
-      <c r="P13" s="101" t="inlineStr">
+      <c r="P13" s="119" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN SUROESTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>SUROESTE</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="79">
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="97">
         <v>56.0923478942375</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="99">
         <v>57.2431051746896</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="101">
         <v>23.884697928268</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="103">
         <v>15.5448856628718</v>
       </c>
-      <c r="I14" s="87">
+      <c r="I14" s="105">
         <v>48.1050430278843</v>
       </c>
-      <c r="J14" s="89">
+      <c r="J14" s="107">
         <v>22.6604661654911</v>
       </c>
-      <c r="K14" s="91">
+      <c r="K14" s="109">
         <v>32.1878198088108</v>
       </c>
-      <c r="L14" s="93">
+      <c r="L14" s="111">
         <v>10.1916153631976</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="113">
         <v>74.6436953450481</v>
       </c>
-      <c r="N14" s="97">
+      <c r="N14" s="115">
         <v>17.4565361650786</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="117">
         <v>65.0516486584922</v>
       </c>
-      <c r="P14" s="101">
+      <c r="P14" s="119">
         <v>100</v>
       </c>
     </row>
@@ -8555,35 +9139,35 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -8608,7 +9192,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -8631,7 +9215,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.292307692307692</v>
       </c>
     </row>
@@ -8654,7 +9238,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.188976377952756</v>
       </c>
     </row>
@@ -8677,7 +9261,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.557692307692308</v>
       </c>
     </row>
@@ -8700,7 +9284,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.557377049180328</v>
       </c>
     </row>
@@ -8723,7 +9307,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="123">
         <v>0.241935483870968</v>
       </c>
     </row>
@@ -8746,7 +9330,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="102">
+      <c r="E8" s="123">
         <v>0.331967213114754</v>
       </c>
     </row>
@@ -8769,7 +9353,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="102">
+      <c r="E9" s="123">
         <v>0.337078651685393</v>
       </c>
     </row>
@@ -8792,7 +9376,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="123">
         <v>0.472727272727273</v>
       </c>
     </row>
@@ -8815,7 +9399,7 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="102">
+      <c r="E11" s="123">
         <v>0.560975609756098</v>
       </c>
     </row>
@@ -8838,32 +9422,32 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="102">
+      <c r="E12" s="123">
         <v>0.377358490566038</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="103">
+      <c r="C13" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="124">
         <v>0.386520862016995</v>
       </c>
     </row>
@@ -8879,53 +9463,53 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -8950,17 +9534,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>1815</v>
-      </c>
-      <c r="F2" s="106">
-        <v>1570</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.865013774104683</v>
-      </c>
-      <c r="H2" s="110">
-        <v>403.422982885086</v>
+      <c r="E2" s="128">
+        <v>552</v>
+      </c>
+      <c r="F2" s="130">
+        <v>477</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.864130434782609</v>
+      </c>
+      <c r="H2" s="134">
+        <v>122.693931984886</v>
       </c>
     </row>
     <row r="3">
@@ -8982,17 +9566,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>14136</v>
-      </c>
-      <c r="F3" s="106">
-        <v>9708</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.686757215619694</v>
-      </c>
-      <c r="H3" s="110">
-        <v>535.434263853642</v>
+      <c r="E3" s="128">
+        <v>4593</v>
+      </c>
+      <c r="F3" s="130">
+        <v>3315</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.721750489875898</v>
+      </c>
+      <c r="H3" s="134">
+        <v>173.970682928677</v>
       </c>
     </row>
     <row r="4">
@@ -9014,17 +9598,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>5851</v>
-      </c>
-      <c r="F4" s="106">
-        <v>3383</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.57819176209195</v>
-      </c>
-      <c r="H4" s="110">
-        <v>406.997774067891</v>
+      <c r="E4" s="128">
+        <v>2129</v>
+      </c>
+      <c r="F4" s="130">
+        <v>1352</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.635039924847346</v>
+      </c>
+      <c r="H4" s="134">
+        <v>148.094045631608</v>
       </c>
     </row>
     <row r="5">
@@ -9046,17 +9630,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>2798</v>
-      </c>
-      <c r="F5" s="106">
-        <v>2135</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.763045032165833</v>
-      </c>
-      <c r="H5" s="110">
-        <v>323.318696556506</v>
+      <c r="E5" s="128">
+        <v>1213</v>
+      </c>
+      <c r="F5" s="130">
+        <v>1009</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0.831821929101402</v>
+      </c>
+      <c r="H5" s="134">
+        <v>140.16639704183</v>
       </c>
     </row>
     <row r="6">
@@ -9078,17 +9662,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>1324</v>
-      </c>
-      <c r="F6" s="106">
-        <v>417</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.314954682779456</v>
-      </c>
-      <c r="H6" s="110">
-        <v>202.508412358519</v>
+      <c r="E6" s="128">
+        <v>354</v>
+      </c>
+      <c r="F6" s="130">
+        <v>120</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.338983050847458</v>
+      </c>
+      <c r="H6" s="134">
+        <v>54.1449984704803</v>
       </c>
     </row>
     <row r="7">
@@ -9110,17 +9694,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="104">
-        <v>1589</v>
-      </c>
-      <c r="F7" s="106">
-        <v>1108</v>
-      </c>
-      <c r="G7" s="108">
-        <v>0.697293895531781</v>
-      </c>
-      <c r="H7" s="110">
-        <v>175.521926433227</v>
+      <c r="E7" s="128">
+        <v>471</v>
+      </c>
+      <c r="F7" s="130">
+        <v>286</v>
+      </c>
+      <c r="G7" s="132">
+        <v>0.607218683651805</v>
+      </c>
+      <c r="H7" s="134">
+        <v>52.0269523914724</v>
       </c>
     </row>
     <row r="8">
@@ -9142,17 +9726,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="104">
-        <v>12934</v>
-      </c>
-      <c r="F8" s="106">
-        <v>9694</v>
-      </c>
-      <c r="G8" s="108">
-        <v>0.749497448585124</v>
-      </c>
-      <c r="H8" s="110">
-        <v>438.887003732609</v>
+      <c r="E8" s="128">
+        <v>3544</v>
+      </c>
+      <c r="F8" s="130">
+        <v>2564</v>
+      </c>
+      <c r="G8" s="132">
+        <v>0.723476297968397</v>
+      </c>
+      <c r="H8" s="134">
+        <v>120.25788937903</v>
       </c>
     </row>
     <row r="9">
@@ -9174,17 +9758,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="104">
-        <v>5325</v>
-      </c>
-      <c r="F9" s="106">
-        <v>3082</v>
-      </c>
-      <c r="G9" s="108">
-        <v>0.578779342723005</v>
-      </c>
-      <c r="H9" s="110">
-        <v>319.359481827996</v>
+      <c r="E9" s="128">
+        <v>1262</v>
+      </c>
+      <c r="F9" s="130">
+        <v>627</v>
+      </c>
+      <c r="G9" s="132">
+        <v>0.496830427892235</v>
+      </c>
+      <c r="H9" s="134">
+        <v>75.6866978529447</v>
       </c>
     </row>
     <row r="10">
@@ -9206,17 +9790,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="104">
-        <v>2936</v>
-      </c>
-      <c r="F10" s="106">
-        <v>1457</v>
-      </c>
-      <c r="G10" s="108">
-        <v>0.49625340599455</v>
-      </c>
-      <c r="H10" s="110">
-        <v>447.834045149481</v>
+      <c r="E10" s="128">
+        <v>799</v>
+      </c>
+      <c r="F10" s="130">
+        <v>391</v>
+      </c>
+      <c r="G10" s="132">
+        <v>0.48936170212766</v>
+      </c>
+      <c r="H10" s="134">
+        <v>121.873093349603</v>
       </c>
     </row>
     <row r="11">
@@ -9238,17 +9822,17 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="104">
-        <v>1768</v>
-      </c>
-      <c r="F11" s="106">
-        <v>1327</v>
-      </c>
-      <c r="G11" s="108">
-        <v>0.750565610859729</v>
-      </c>
-      <c r="H11" s="110">
-        <v>263.33035448317</v>
+      <c r="E11" s="128">
+        <v>584</v>
+      </c>
+      <c r="F11" s="130">
+        <v>423</v>
+      </c>
+      <c r="G11" s="132">
+        <v>0.724315068493151</v>
+      </c>
+      <c r="H11" s="134">
+        <v>86.9824247840334</v>
       </c>
     </row>
     <row r="12">
@@ -9270,51 +9854,51 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="104">
-        <v>8958</v>
-      </c>
-      <c r="F12" s="106">
-        <v>7163</v>
-      </c>
-      <c r="G12" s="108">
-        <v>0.799620450993525</v>
-      </c>
-      <c r="H12" s="110">
-        <v>721.720915243313</v>
+      <c r="E12" s="128">
+        <v>1787</v>
+      </c>
+      <c r="F12" s="130">
+        <v>1262</v>
+      </c>
+      <c r="G12" s="132">
+        <v>0.706211527700056</v>
+      </c>
+      <c r="H12" s="134">
+        <v>143.973573960683</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA CARTAMA</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="105">
-        <v>5403.09090909091</v>
-      </c>
-      <c r="F13" s="107">
-        <v>3731.27272727273</v>
-      </c>
-      <c r="G13" s="109">
-        <v>0.66181569285903</v>
-      </c>
-      <c r="H13" s="111">
-        <v>385.303259690131</v>
+      <c r="A13" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C13" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="129">
+        <v>17288</v>
+      </c>
+      <c r="F13" s="131">
+        <v>11826</v>
+      </c>
+      <c r="G13" s="133">
+        <v>0.684058306339658</v>
+      </c>
+      <c r="H13" s="135">
+        <v>122.308927674447</v>
       </c>
     </row>
   </sheetData>
